--- a/public_administration_forms/008_government_service_satisfaction_poll--public_administration_forms.xlsx
+++ b/public_administration_forms/008_government_service_satisfaction_poll--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>highly_likely</t>
+          <t>highly likely</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>in person</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>less_than_1_year</t>
+          <t>less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1_year_or_more</t>
+          <t>1 year or more</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5_years_or_more</t>
+          <t>5 years or more</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>more_than_5_years</t>
+          <t>more than 5 years</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>less than 1 month</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1_month_or_more</t>
+          <t>1 month or more</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1_year_or_more</t>
+          <t>1 year or more</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>more_than_1_year</t>
+          <t>more than 1 year</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>highly_likely</t>
+          <t>highly likely</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>graduate_school</t>
+          <t>graduate school</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>postgraduate_school</t>
+          <t>postgraduate school</t>
         </is>
       </c>
     </row>
